--- a/data/trans_orig/P32B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271515</t>
+          <t>269733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279838</t>
+          <t>279826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176934</t>
+          <t>176483</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185239</t>
+          <t>185235</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>451193</t>
+          <t>452803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>463869</t>
+          <t>464102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493584</t>
+          <t>493302</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500040</t>
+          <t>500033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211125</t>
+          <t>210202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707507</t>
+          <t>708012</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>716325</t>
+          <t>716321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>395467</t>
+          <t>395244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219108</t>
+          <t>219664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617765</t>
+          <t>617575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625185</t>
+          <t>625196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,97 +1762,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5840</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1173</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6010</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7816</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1173</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5901</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>311461</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313494</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139193</t>
+          <t>139363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>452796</t>
+          <t>450881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,39 +2120,39 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5346</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167426</t>
+          <t>166118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177623</t>
+          <t>177293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,42 +2233,42 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>74406</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>68399</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>75436</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>98,63%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>74406</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>70090</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>75436</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239897</t>
+          <t>240697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252120</t>
+          <t>252561</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>127941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157340</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>159191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,62 +2826,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2083</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5670</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4996</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68027</t>
+          <t>68073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84664</t>
+          <t>83990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,82 +3149,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4583</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>18108</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>16469</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>36675</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>16261</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>15956</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>35383</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1855169</t>
+          <t>1855208</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1871384</t>
+          <t>1870699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,82 +3262,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>876412</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>889937</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2749765</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2737764</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2757970</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>878259</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>890459</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2749765</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>2739056</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2758483</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24954</t>
+          <t>23833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255569</t>
+          <t>256690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271172</t>
+          <t>271112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172055</t>
+          <t>172283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181524</t>
+          <t>181549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>433713</t>
+          <t>434794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>450643</t>
+          <t>451753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>25696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443492</t>
+          <t>443087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>459740</t>
+          <t>459607</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207800</t>
+          <t>208327</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>656178</t>
+          <t>655535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>672544</t>
+          <t>672791</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>20752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>23161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406832</t>
+          <t>407309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421205</t>
+          <t>421651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>240249</t>
+          <t>239671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649182</t>
+          <t>649262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664836</t>
+          <t>665262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381242</t>
+          <t>381584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>392000</t>
+          <t>391961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211197</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213375</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594193</t>
+          <t>594276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>604879</t>
+          <t>605341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219150</t>
+          <t>217422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230959</t>
+          <t>230952</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331542</t>
+          <t>331675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343164</t>
+          <t>343038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142527</t>
+          <t>142601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153450</t>
+          <t>153457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55368</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57482</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>199970</t>
+          <t>198814</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>210964</t>
+          <t>210912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,62 +5805,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2294</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>12142</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>12360</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74909</t>
+          <t>75816</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24368</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>97758</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43502</t>
+          <t>44262</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74590</t>
+          <t>77238</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50990</t>
+          <t>49859</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84477</t>
+          <t>82695</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1967654</t>
+          <t>1965006</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1998742</t>
+          <t>1997982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1034300</t>
+          <t>1034215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1045694</t>
+          <t>1045620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3006503</t>
+          <t>3008285</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3039990</t>
+          <t>3041121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>17013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242903</t>
+          <t>242805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254003</t>
+          <t>253407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161749</t>
+          <t>162623</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>169779</t>
+          <t>169788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>409684</t>
+          <t>409970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>422140</t>
+          <t>422009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345090</t>
+          <t>344678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358763</t>
+          <t>358838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>214995</t>
+          <t>215765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223642</t>
+          <t>223668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>564603</t>
+          <t>565017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>581181</t>
+          <t>581288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>417758</t>
+          <t>417157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429244</t>
+          <t>428411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242342</t>
+          <t>242276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663379</t>
+          <t>663291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>676084</t>
+          <t>675930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>370442</t>
+          <t>371391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>384952</t>
+          <t>385073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258474</t>
+          <t>258428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634038</t>
+          <t>634522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649721</t>
+          <t>649411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>272659</t>
+          <t>274581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285616</t>
+          <t>284900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129528</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403481</t>
+          <t>403560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6095</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172600</t>
+          <t>172614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65516</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67603</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>241126</t>
+          <t>238992</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,62 +8784,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3914</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4002</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91690</t>
+          <t>90870</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127999</t>
+          <t>128087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57266</t>
+          <t>58754</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>19812</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71195</t>
+          <t>69369</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1945348</t>
+          <t>1943860</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1971990</t>
+          <t>1972406</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1125470</t>
+          <t>1124933</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1138781</t>
+          <t>1138266</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3076164</t>
+          <t>3077990</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3107528</t>
+          <t>3106429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023 (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169034</t>
+          <t>169085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87378</t>
+          <t>88047</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100682</t>
+          <t>100688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>256189</t>
+          <t>256636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270284</t>
+          <t>270429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,42 +10068,42 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>11326</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>4037</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>22679</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>11326</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>4078</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206279</t>
+          <t>206212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226559</t>
+          <t>226809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137931</t>
+          <t>137734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,47 +10176,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>361062</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>349709</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>368351</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>96,96%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>361062</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>348125</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>368310</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273875</t>
+          <t>271616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280830</t>
+          <t>280828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144491</t>
+          <t>144563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149652</t>
+          <t>149650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>420676</t>
+          <t>421072</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>429336</t>
+          <t>429303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334438</t>
+          <t>334391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342922</t>
+          <t>343060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186051</t>
+          <t>186094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191122</t>
+          <t>191116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>523108</t>
+          <t>523059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>533318</t>
+          <t>533425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20140</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246540</t>
+          <t>246685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>258124</t>
+          <t>258519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127496</t>
+          <t>127175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133497</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377631</t>
+          <t>377802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>389925</t>
+          <t>390075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>366</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182513</t>
+          <t>183289</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188337</t>
+          <t>188618</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275879</t>
+          <t>275981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>460903</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468374</t>
+          <t>468328</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94372</t>
+          <t>94746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24420</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>121398</t>
+          <t>121297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126070</t>
+          <t>126053</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20826</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,47 +12086,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>13525</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>5925</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>23663</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>13525</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>6984</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>24659</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1531526</t>
+          <t>1529215</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1556818</t>
+          <t>1556296</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,47 +12199,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1012322</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1002184</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1019922</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1012322</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1001188</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1018863</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2542255</t>
+          <t>2541718</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2573538</t>
+          <t>2574198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269733</t>
+          <t>270814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279826</t>
+          <t>279832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176483</t>
+          <t>176830</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185235</t>
+          <t>185237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>452803</t>
+          <t>451656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>464102</t>
+          <t>463783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493302</t>
+          <t>493184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500033</t>
+          <t>500029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210202</t>
+          <t>210043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708012</t>
+          <t>707771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>716321</t>
+          <t>716280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>395244</t>
+          <t>395193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219664</t>
+          <t>218774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617575</t>
+          <t>618388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625196</t>
+          <t>626061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139363</t>
+          <t>139417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>450881</t>
+          <t>451769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166118</t>
+          <t>165388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177293</t>
+          <t>177392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68399</t>
+          <t>71230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240697</t>
+          <t>239906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252561</t>
+          <t>251930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68073</t>
+          <t>68064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,82 +3149,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>17607</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>16605</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>36431</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>18108</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>16469</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>36675</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1855208</t>
+          <t>1855499</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1870699</t>
+          <t>1871485</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,82 +3262,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>876913</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>889594</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2749765</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2738008</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2757834</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>876412</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>889937</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2749765</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>2737764</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2757970</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256690</t>
+          <t>256706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>271112</t>
+          <t>271430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172283</t>
+          <t>170263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181549</t>
+          <t>181425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>434794</t>
+          <t>433881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>451753</t>
+          <t>451020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25696</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443087</t>
+          <t>442026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>459607</t>
+          <t>459684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208327</t>
+          <t>208048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655535</t>
+          <t>656006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>672791</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407309</t>
+          <t>407194</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421651</t>
+          <t>421642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239671</t>
+          <t>239531</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649262</t>
+          <t>650556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>665262</t>
+          <t>665105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381584</t>
+          <t>380981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>391961</t>
+          <t>391951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594276</t>
+          <t>594938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>605341</t>
+          <t>604551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217422</t>
+          <t>217491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230952</t>
+          <t>230972</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331675</t>
+          <t>328918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343038</t>
+          <t>343166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142601</t>
+          <t>142543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153457</t>
+          <t>153459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198814</t>
+          <t>199574</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>210912</t>
+          <t>210935</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>74115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97758</t>
+          <t>98801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>42163</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77238</t>
+          <t>75862</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49859</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82695</t>
+          <t>84351</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1965006</t>
+          <t>1966382</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1997982</t>
+          <t>2000081</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1034215</t>
+          <t>1033964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1045620</t>
+          <t>1045635</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3008285</t>
+          <t>3006629</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3041121</t>
+          <t>3040777</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242805</t>
+          <t>242978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253407</t>
+          <t>254000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162623</t>
+          <t>161843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>169788</t>
+          <t>169775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>409970</t>
+          <t>410307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>422009</t>
+          <t>422712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>19750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26209</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344678</t>
+          <t>345939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358838</t>
+          <t>358699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>215765</t>
+          <t>215112</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223668</t>
+          <t>223711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>565017</t>
+          <t>565043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>581288</t>
+          <t>581192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>417157</t>
+          <t>417574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>428411</t>
+          <t>428388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242276</t>
+          <t>242362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663291</t>
+          <t>663676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675930</t>
+          <t>676061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371391</t>
+          <t>370575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>385073</t>
+          <t>384898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258428</t>
+          <t>258533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634522</t>
+          <t>634966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649411</t>
+          <t>649667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274581</t>
+          <t>274845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>284900</t>
+          <t>285631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403560</t>
+          <t>404448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>415169</t>
+          <t>414434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172614</t>
+          <t>172239</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238992</t>
+          <t>239726</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90870</t>
+          <t>90857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>128087</t>
+          <t>127457</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58754</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40930</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69369</t>
+          <t>69605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1943860</t>
+          <t>1944884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1972406</t>
+          <t>1971385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1124933</t>
+          <t>1124430</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1138266</t>
+          <t>1138533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3077990</t>
+          <t>3077754</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3106429</t>
+          <t>3106400</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>169738</t>
+          <t>164590</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169085</t>
+          <t>157472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>96850</t>
+          <t>106663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>96533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100688</t>
+          <t>111142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>266587</t>
+          <t>271253</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>256636</t>
+          <t>261335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270429</t>
+          <t>276917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23923</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>24392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>219666</t>
+          <t>238549</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206212</t>
+          <t>225896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226809</t>
+          <t>245103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>141396</t>
+          <t>152130</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137734</t>
+          <t>148533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>361062</t>
+          <t>390679</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349709</t>
+          <t>378063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368351</t>
+          <t>397605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>278534</t>
+          <t>307057</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271616</t>
+          <t>300148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280828</t>
+          <t>310500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148138</t>
+          <t>167062</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>163442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149650</t>
+          <t>168689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>426672</t>
+          <t>474117</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>421072</t>
+          <t>467414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>429303</t>
+          <t>477965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>340017</t>
+          <t>348824</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334391</t>
+          <t>342451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343060</t>
+          <t>351929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>189586</t>
+          <t>208695</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186094</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191116</t>
+          <t>210810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>529603</t>
+          <t>557518</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>523059</t>
+          <t>550482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>533425</t>
+          <t>562103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191903</t>
+          <t>212012</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191903</t>
+          <t>212012</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191903</t>
+          <t>212012</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>536007</t>
+          <t>565766</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>536007</t>
+          <t>565766</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>536007</t>
+          <t>565766</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>20786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>253748</t>
+          <t>271568</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246685</t>
+          <t>264541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>258519</t>
+          <t>275979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>131213</t>
+          <t>144145</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127175</t>
+          <t>140121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133236</t>
+          <t>146297</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>384961</t>
+          <t>415713</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377802</t>
+          <t>407819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390075</t>
+          <t>420766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11425,12 +11425,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>186775</t>
+          <t>203806</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183289</t>
+          <t>199736</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188618</t>
+          <t>205988</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,27 +11528,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>278949</t>
+          <t>79049</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275981</t>
+          <t>76767</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>465724</t>
+          <t>282855</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461166</t>
+          <t>278124</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468328</t>
+          <t>285100</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>286598</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>286598</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>286598</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>98219</t>
+          <t>107826</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94746</t>
+          <t>104351</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99491</t>
+          <t>109192</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>124411</t>
+          <t>137515</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>121297</t>
+          <t>133878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126053</t>
+          <t>139306</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>53349</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>53510</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>74234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1546697</t>
+          <t>1642218</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1529215</t>
+          <t>1625235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1556296</t>
+          <t>1653389</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1012322</t>
+          <t>887432</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1002184</t>
+          <t>874581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1019922</t>
+          <t>894420</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2559019</t>
+          <t>2529650</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2541718</t>
+          <t>2508926</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2574198</t>
+          <t>2542994</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
